--- a/engines/kg/Original Data source/Course Catalogue_Correct Version.xlsx
+++ b/engines/kg/Original Data source/Course Catalogue_Correct Version.xlsx
@@ -526,7 +526,7 @@
     <t>Machine Learning Fundamentals</t>
   </si>
   <si>
-    <t>C-CS21
+    <t>C-CS215
 C-ST211</t>
   </si>
   <si>
@@ -631,7 +631,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
   <numFmts count="0"/>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -642,6 +642,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -678,16 +684,16 @@
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general" wrapText="1"/>
-    </xf>
     <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
@@ -1040,7 +1046,7 @@
         <v>7</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -1066,7 +1072,7 @@
         <v>13</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
       <c r="A3" s="1" t="s">
         <v>14</v>
       </c>
@@ -1092,7 +1098,7 @@
         <v>17</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="4" customHeight="1" ht="19.5">
       <c r="A4" s="1" t="s">
         <v>18</v>
       </c>
@@ -1118,7 +1124,7 @@
         <v>21</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="5" customHeight="1" ht="19.5">
       <c r="A5" s="1" t="s">
         <v>22</v>
       </c>
@@ -1144,7 +1150,7 @@
         <v>24</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="6" customHeight="1" ht="19.5">
       <c r="A6" s="1" t="s">
         <v>25</v>
       </c>
@@ -1168,7 +1174,7 @@
       </c>
       <c r="H6" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="7" customHeight="1" ht="19.5">
       <c r="A7" s="1" t="s">
         <v>27</v>
       </c>
@@ -1192,7 +1198,7 @@
       </c>
       <c r="H7" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="8" customHeight="1" ht="19.5">
       <c r="A8" s="1" t="s">
         <v>29</v>
       </c>
@@ -1218,7 +1224,7 @@
         <v>31</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="9" customHeight="1" ht="19.5">
       <c r="A9" s="1" t="s">
         <v>32</v>
       </c>
@@ -1242,7 +1248,7 @@
       </c>
       <c r="H9" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="10" customHeight="1" ht="45">
       <c r="A10" s="1" t="s">
         <v>35</v>
       </c>
@@ -1268,7 +1274,7 @@
         <v>37</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="11" customHeight="1" ht="19.5">
       <c r="A11" s="1" t="s">
         <v>38</v>
       </c>
@@ -1294,7 +1300,7 @@
         <v>40</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="12" customHeight="1" ht="31.5">
       <c r="A12" s="1" t="s">
         <v>41</v>
       </c>
@@ -1320,7 +1326,7 @@
         <v>44</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="13" customHeight="1" ht="19.5">
       <c r="A13" s="1" t="s">
         <v>45</v>
       </c>
@@ -1346,7 +1352,7 @@
         <v>47</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="14" customHeight="1" ht="19.5">
       <c r="A14" s="1" t="s">
         <v>48</v>
       </c>
@@ -1372,7 +1378,7 @@
         <v>50</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="19.5">
       <c r="A15" s="1" t="s">
         <v>51</v>
       </c>
@@ -1398,7 +1404,7 @@
         <v>53</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="16" customHeight="1" ht="19.5">
       <c r="A16" s="1" t="s">
         <v>54</v>
       </c>
@@ -1424,7 +1430,7 @@
         <v>56</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="17" customHeight="1" ht="19.5">
       <c r="A17" s="1" t="s">
         <v>57</v>
       </c>
@@ -1450,7 +1456,7 @@
         <v>59</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="18" customHeight="1" ht="31.5">
       <c r="A18" s="1" t="s">
         <v>60</v>
       </c>
@@ -1476,7 +1482,7 @@
         <v>63</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="19" customHeight="1" ht="19.5">
       <c r="A19" s="1" t="s">
         <v>64</v>
       </c>
@@ -1502,7 +1508,7 @@
         <v>66</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="20" customHeight="1" ht="19.5">
       <c r="A20" s="1" t="s">
         <v>67</v>
       </c>
@@ -1528,7 +1534,7 @@
         <v>69</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="21" customHeight="1" ht="19.5">
       <c r="A21" s="1" t="s">
         <v>70</v>
       </c>
@@ -1554,7 +1560,7 @@
         <v>72</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="18.75">
+    <row x14ac:dyDescent="0.25" r="22" customHeight="1" ht="31.5">
       <c r="A22" s="1" t="s">
         <v>73</v>
       </c>
